--- a/data/trending_integrated_20260923_10.xlsx
+++ b/data/trending_integrated_20260923_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30734129738</v>
+        <v>31011083303</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3연상 기록 후 지속적인 상승세. 의료 AI 및 미국 AI 주가 급등 모멘텀.</t>
+          <t>3연상 기록 및 AI 관련 테마 기대감. 긍정적인 흐름 유지 속 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['3연상', '의료AI', '모멘텀']</t>
+          <t>['3연상', 'AI', '테마']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18590</v>
+        <v>18850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.39%</t>
+          <t>'+13.97%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>222171206840</v>
+        <v>228428291700</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 관련주 급등에 따른 국내 양자 보안주 동반 상승 기대. 공매도 세력과의 신경전.</t>
+          <t>미국 양자 관련주 급등에 따른 기대감. 공매도 세력과의 갈등 및 단기 급등 가능성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2970</v>
+        <v>3060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.95%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H4" t="n">
         <v>1.4</v>
@@ -794,7 +794,7 @@
         <v>0.48</v>
       </c>
       <c r="O4" t="n">
-        <v>17173891463</v>
+        <v>17690746299</v>
       </c>
       <c r="P4" t="n">
         <v>4760</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>잦은 유상증자 및 공매도 관련 의문 제기. 차트상 약세 보임.</t>
+          <t>유상증자 관련 의문 제기 및 모더나 관련 기대감 혼재. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유상증자', '공매도', '차트']</t>
+          <t>['유상증자', '모더나', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8710</v>
+        <v>219000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="H5" t="n">
-        <v>26.63</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8470</v>
+        <v>211500</v>
       </c>
       <c r="K5" t="n">
-        <v>8510</v>
+        <v>217000</v>
       </c>
       <c r="L5" t="n">
-        <v>8870</v>
+        <v>220000</v>
       </c>
       <c r="M5" t="n">
-        <v>8480</v>
+        <v>216500</v>
       </c>
       <c r="N5" t="n">
-        <v>26.58</v>
+        <v>75.5</v>
       </c>
       <c r="O5" t="n">
-        <v>11618979860</v>
+        <v>409902435250</v>
       </c>
       <c r="P5" t="n">
-        <v>17950</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>8120</v>
+        <v>65000</v>
       </c>
       <c r="R5" t="n">
-        <v>359000</v>
+        <v>276000</v>
       </c>
       <c r="S5" t="n">
-        <v>23000</v>
+        <v>-25000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>LG 로봇 사업 재평가로 인한 그룹주 동반 상승 기대감. 부채 상환 부담 및 적자 지속 우려.</t>
+          <t>배당금 기대감과 우선주 소각 이슈. 30만원 돌파 및 신고가 경신 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', '재평가', '부채']</t>
+          <t>['배당', '우선주', '신고가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13980</v>
+        <v>8720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.79%</t>
+          <t>'+2.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.16</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H6" t="n">
-        <v>9.609999999999999</v>
+        <v>26.63</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13600</v>
+        <v>8470</v>
       </c>
       <c r="K6" t="n">
-        <v>13750</v>
+        <v>8510</v>
       </c>
       <c r="L6" t="n">
-        <v>15050</v>
+        <v>8870</v>
       </c>
       <c r="M6" t="n">
-        <v>13750</v>
+        <v>8480</v>
       </c>
       <c r="N6" t="n">
-        <v>9.77</v>
+        <v>26.58</v>
       </c>
       <c r="O6" t="n">
-        <v>75290793555</v>
+        <v>12285392860</v>
       </c>
       <c r="P6" t="n">
-        <v>23550</v>
+        <v>17950</v>
       </c>
       <c r="Q6" t="n">
-        <v>5780</v>
+        <v>8120</v>
       </c>
       <c r="R6" t="n">
-        <v>275000</v>
+        <v>359000</v>
       </c>
       <c r="S6" t="n">
-        <v>-64000</v>
+        <v>23000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속에 따른 주가 하락 우려. 주가 조작 의혹 제기.</t>
+          <t>부정적인 재무 상태에도 불구하고 투자 심리 유지. LG 로봇 관련 테마 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기관', '외인', '매도세']</t>
+          <t>['적자', '부채', '로봇']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>283000</v>
+        <v>14000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>461</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>2971</v>
+        <v>136</v>
       </c>
       <c r="H7" t="n">
-        <v>46.55</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>276500</v>
+        <v>13600</v>
       </c>
       <c r="K7" t="n">
-        <v>284500</v>
+        <v>13750</v>
       </c>
       <c r="L7" t="n">
-        <v>285000</v>
+        <v>15050</v>
       </c>
       <c r="M7" t="n">
-        <v>282500</v>
+        <v>13750</v>
       </c>
       <c r="N7" t="n">
-        <v>46.56</v>
+        <v>9.77</v>
       </c>
       <c r="O7" t="n">
-        <v>1518325837250</v>
+        <v>77296060485</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>23550</v>
       </c>
       <c r="Q7" t="n">
-        <v>82400</v>
+        <v>5780</v>
       </c>
       <c r="R7" t="n">
-        <v>1308000</v>
+        <v>275000</v>
       </c>
       <c r="S7" t="n">
-        <v>346000</v>
+        <v>-64000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 선물 급등에 따른 30만원 돌파 기대감. 추석 연휴 후 상승 전망.</t>
+          <t>기관 및 외인 매도세 지속으로 인한 주가 하락 우려. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '기대감']</t>
+          <t>['기관', '외인', '매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1855000</v>
+        <v>283500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="G8" t="n">
-        <v>1630</v>
+        <v>2577</v>
       </c>
       <c r="H8" t="n">
-        <v>50.15</v>
+        <v>46.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1840000</v>
+        <v>276500</v>
       </c>
       <c r="K8" t="n">
-        <v>1899000</v>
+        <v>284500</v>
       </c>
       <c r="L8" t="n">
-        <v>1900000</v>
+        <v>285000</v>
       </c>
       <c r="M8" t="n">
-        <v>1851000</v>
+        <v>282500</v>
       </c>
       <c r="N8" t="n">
-        <v>50.17</v>
+        <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1594412104500</v>
+        <v>1620627439750</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>333000</v>
+        <v>82400</v>
       </c>
       <c r="R8" t="n">
-        <v>-28000</v>
+        <v>1308000</v>
       </c>
       <c r="S8" t="n">
-        <v>80000</v>
+        <v>346000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 반도체 시장 강세에 따른 주가 상승 기대감. 악재 반영 완료 및 단기 급등 전망.</t>
+          <t>미국 증시 반도체 선물 상승에 따른 기대감. 정치적 언급과 함께 30만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '급등', '기대감']</t>
+          <t>['반도체', '배당', '선물']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17800</v>
+        <v>1865000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+1.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.76</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>486</v>
       </c>
       <c r="G9" t="n">
-        <v>376</v>
+        <v>1490</v>
       </c>
       <c r="H9" t="n">
-        <v>5.46</v>
+        <v>50.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17810</v>
+        <v>1840000</v>
       </c>
       <c r="K9" t="n">
-        <v>17950</v>
+        <v>1899000</v>
       </c>
       <c r="L9" t="n">
-        <v>18180</v>
+        <v>1900000</v>
       </c>
       <c r="M9" t="n">
-        <v>17410</v>
+        <v>1851000</v>
       </c>
       <c r="N9" t="n">
-        <v>6.22</v>
+        <v>50.17</v>
       </c>
       <c r="O9" t="n">
-        <v>88282685945</v>
+        <v>1740102596500</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R9" t="n">
-        <v>-78000</v>
+        <v>-28000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>명절 전 주가 상승 기대감 및 쇼티지 현상 언급. 외인 매도세 관찰.</t>
+          <t>미국 증시와의 격차에 따른 기대감. 200만원 돌파 시도 및 외인 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['쇼티지', '명절', '외인']</t>
+          <t>['반도체', '외인', '200만원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31200</v>
+        <v>17970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.64%</t>
+          <t>'+0.90%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.62</v>
+        <v>-0.76</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>89</v>
+        <v>426</v>
       </c>
       <c r="H10" t="n">
-        <v>52.8</v>
+        <v>5.46</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>31400</v>
+        <v>17810</v>
       </c>
       <c r="K10" t="n">
+        <v>17950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18180</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17410</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="O10" t="n">
+        <v>93595559240</v>
+      </c>
+      <c r="P10" t="n">
         <v>31500</v>
       </c>
-      <c r="L10" t="n">
-        <v>32100</v>
-      </c>
-      <c r="M10" t="n">
-        <v>31100</v>
-      </c>
-      <c r="N10" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="O10" t="n">
-        <v>55209824350</v>
-      </c>
-      <c r="P10" t="n">
-        <v>32100</v>
-      </c>
       <c r="Q10" t="n">
-        <v>21000</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>29000</v>
+        <v>-78000</v>
       </c>
       <c r="S10" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망에 따른 주가 상승 기대. 합병 효과는 장기적.</t>
+          <t>2만원 돌파 기대감 표출과 함께 명절 전 주가 하락 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '기대']</t>
+          <t>['주포', '명절', '거래량']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,86 +1384,86 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30550</v>
+        <v>31150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-0.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>944</v>
+        <v>93</v>
       </c>
       <c r="H11" t="n">
-        <v>16.63</v>
+        <v>52.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>31050</v>
+        <v>31400</v>
       </c>
       <c r="K11" t="n">
-        <v>31300</v>
+        <v>31500</v>
       </c>
       <c r="L11" t="n">
-        <v>31550</v>
+        <v>32100</v>
       </c>
       <c r="M11" t="n">
-        <v>30450</v>
+        <v>31100</v>
       </c>
       <c r="N11" t="n">
-        <v>16.42</v>
+        <v>25.75</v>
       </c>
       <c r="O11" t="n">
-        <v>4349554850</v>
+        <v>57919728175</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>32100</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>21000</v>
       </c>
       <c r="R11" t="n">
-        <v>-27000</v>
+        <v>29000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>릴레이테라퓨틱스 관련 뉴스 및 승인 기대감. 간암/담관암 결과 발표 및 HLB 제약 비교 언급.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망에 따른 주가 상승 기대. 합병 효과는 장기적.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['릴레이테라퓨틱스', '간암', '담관암']</t>
+          <t>['영업이익', '합병', '기대']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23250</v>
+        <v>30700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.92%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="G12" t="n">
-        <v>42</v>
+        <v>959</v>
       </c>
       <c r="H12" t="n">
-        <v>1.68</v>
+        <v>16.63</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>23950</v>
+        <v>31050</v>
       </c>
       <c r="K12" t="n">
-        <v>24400</v>
+        <v>31300</v>
       </c>
       <c r="L12" t="n">
-        <v>25700</v>
+        <v>31550</v>
       </c>
       <c r="M12" t="n">
-        <v>23100</v>
+        <v>30450</v>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>16.42</v>
       </c>
       <c r="O12" t="n">
-        <v>50233902100</v>
+        <v>4578587425</v>
       </c>
       <c r="P12" t="n">
-        <v>39350</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>8200</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>-37000</v>
+        <v>-27000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>타임지 '세계 최고 헬스테크 기업' 선정 관련 기대감. 추세선 분석 및 경쟁사 언급.</t>
+          <t>미국 릴레이테라퓨틱스 상승 및 간암/담관암 신약 FDA 승인 기대감, 과거 패턴 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '추세선']</t>
+          <t>['신약', 'FDA', '승인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83600</v>
+        <v>23300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.35%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>664</v>
+        <v>51</v>
       </c>
       <c r="H13" t="n">
-        <v>23.03</v>
+        <v>1.68</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>86500</v>
+        <v>23950</v>
       </c>
       <c r="K13" t="n">
-        <v>86100</v>
+        <v>24400</v>
       </c>
       <c r="L13" t="n">
-        <v>86100</v>
+        <v>25700</v>
       </c>
       <c r="M13" t="n">
-        <v>83600</v>
+        <v>23050</v>
       </c>
       <c r="N13" t="n">
-        <v>23.05</v>
+        <v>1.76</v>
       </c>
       <c r="O13" t="n">
-        <v>82129726350</v>
+        <v>51606891825</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>39350</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>8200</v>
       </c>
       <c r="R13" t="n">
-        <v>-248000</v>
+        <v>-37000</v>
       </c>
       <c r="S13" t="n">
-        <v>-42000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 한국형 원전 수주 확정 소식에 따른 기대감. 그러나 차트 붕괴 및 원전 시세 종료 가능성 제기.</t>
+          <t>타임지 선정 '세계 최고 헬스테크 기업' 선정 사실 기반, 상장 기대감과 실망감 교차.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '수주', '차트']</t>
+          <t>['헬스테크', '타임지', '상장']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48950</v>
+        <v>83700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.39%</t>
+          <t>'-3.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>240</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="G14" t="n">
-        <v>77</v>
+        <v>731</v>
       </c>
       <c r="H14" t="n">
-        <v>38.34</v>
+        <v>23.03</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>51200</v>
+        <v>86500</v>
       </c>
       <c r="K14" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="L14" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="M14" t="n">
-        <v>48800</v>
+        <v>83500</v>
       </c>
       <c r="N14" t="n">
-        <v>38.44</v>
+        <v>23.05</v>
       </c>
       <c r="O14" t="n">
-        <v>44793650300</v>
+        <v>91575594950</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-182000</v>
+        <v>-248000</v>
       </c>
       <c r="S14" t="n">
-        <v>-21000</v>
+        <v>-42000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>수조원 규모 수주에도 불구하고 주가 하락 지속. 20일선 지지 실패 및 IR 효과 미미.</t>
+          <t>미국 원전 관련 호재에도 불구하고 주가 하락 우려. 차트 붕괴 및 테마 소멸 가능성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '주가하락', '지지선']</t>
+          <t>['원전', 'SMR', '호재']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17720</v>
+        <v>49350</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.74%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="H15" t="n">
-        <v>10.38</v>
+        <v>38.34</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,58 +1791,150 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18800</v>
+        <v>51200</v>
       </c>
       <c r="K15" t="n">
-        <v>18800</v>
+        <v>51600</v>
       </c>
       <c r="L15" t="n">
-        <v>18800</v>
+        <v>51600</v>
       </c>
       <c r="M15" t="n">
-        <v>17600</v>
+        <v>48800</v>
       </c>
       <c r="N15" t="n">
-        <v>10.47</v>
+        <v>38.44</v>
       </c>
       <c r="O15" t="n">
-        <v>73601036715</v>
+        <v>48473800450</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>-1005000</v>
+        <v>-182000</v>
       </c>
       <c r="S15" t="n">
-        <v>-51000</v>
+        <v>-21000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 건설/원전 수주 기대감 및 공매도 세력과의 갈등 심화. 대차해지 운동 촉구.</t>
+          <t>대규모 수주에도 불구하고 주가 하락 지속. IR 담당자의 주가 상승 관련 소통 부재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['건설', '원전', '공매도']</t>
+          <t>['수주', '주가하락', 'IR']</t>
         </is>
       </c>
       <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>17720</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-5.74%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E16" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" t="n">
+        <v>64</v>
+      </c>
+      <c r="G16" t="n">
+        <v>295</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K16" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17600</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O16" t="n">
+        <v>77394029805</v>
+      </c>
+      <c r="P16" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1005000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>미국 건설 및 원전 상승에 따른 기대감. 공매도 세력과의 갈등 및 대차 해지 운동.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['공매도', '원전', '대차']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
         <v>22</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20260923_10.xlsx
+++ b/data/trending_integrated_20260923_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31011083303</v>
+        <v>31131132533</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3연상 기록 및 AI 관련 테마 기대감. 긍정적인 흐름 유지 속 추가 상승 전망.</t>
+          <t>3연상 기록 및 AI 관련 기대감. 추가 상승 및 단기 폭락 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['3연상', 'AI', '테마']</t>
+          <t>['3연상', 'AI', '단기폭락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18850</v>
+        <v>18730</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.97%</t>
+          <t>'+13.24%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>228428291700</v>
+        <v>232050409745</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 기대감. 공매도 세력과의 갈등 및 단기 급등 가능성.</t>
+          <t>미국 양자 관련주 급등에 따른 기대감. 공매도 세력에 대한 경계.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자', '보안', '공매도']</t>
+          <t>['양자보안', '공매도', '아이온큐']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3060</v>
+        <v>220000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.92</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2885</v>
+        <v>211500</v>
       </c>
       <c r="K4" t="n">
-        <v>3000</v>
+        <v>217000</v>
       </c>
       <c r="L4" t="n">
-        <v>3480</v>
+        <v>220000</v>
       </c>
       <c r="M4" t="n">
-        <v>2885</v>
+        <v>216500</v>
       </c>
       <c r="N4" t="n">
-        <v>0.48</v>
+        <v>75.5</v>
       </c>
       <c r="O4" t="n">
-        <v>17690746299</v>
+        <v>452791949000</v>
       </c>
       <c r="P4" t="n">
-        <v>4760</v>
+        <v>243500</v>
       </c>
       <c r="Q4" t="n">
-        <v>973</v>
+        <v>65000</v>
       </c>
       <c r="R4" t="n">
-        <v>-235000</v>
+        <v>276000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유상증자 관련 의문 제기 및 모더나 관련 기대감 혼재. 공매도 세력에 대한 언급.</t>
+          <t>장기 보유 및 배당금 증액 기대. 특별 배당 및 소각 이슈 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유상증자', '모더나', '공매도']</t>
+          <t>['장기보유', '배당금', '특별배당']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219000</v>
+        <v>2995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+3.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>0.92</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="H5" t="n">
-        <v>75.51000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>211500</v>
+        <v>2885</v>
       </c>
       <c r="K5" t="n">
-        <v>217000</v>
+        <v>3000</v>
       </c>
       <c r="L5" t="n">
-        <v>220000</v>
+        <v>3480</v>
       </c>
       <c r="M5" t="n">
-        <v>216500</v>
+        <v>2885</v>
       </c>
       <c r="N5" t="n">
-        <v>75.5</v>
+        <v>0.48</v>
       </c>
       <c r="O5" t="n">
-        <v>409902435250</v>
+        <v>17958393641</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>4760</v>
       </c>
       <c r="Q5" t="n">
-        <v>65000</v>
+        <v>973</v>
       </c>
       <c r="R5" t="n">
-        <v>276000</v>
+        <v>-235000</v>
       </c>
       <c r="S5" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>배당금 기대감과 우선주 소각 이슈. 30만원 돌파 및 신고가 경신 기대.</t>
+          <t>유상증자 관련 논란 속 주가 반등 시도. 2분기 중간 분석 결과 발표 예정.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['배당', '우선주', '신고가']</t>
+          <t>['유상증자', '주가', '분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8720</v>
+        <v>8740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.95%</t>
+          <t>'+3.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="H6" t="n">
         <v>26.63</v>
@@ -978,7 +978,7 @@
         <v>26.58</v>
       </c>
       <c r="O6" t="n">
-        <v>12285392860</v>
+        <v>12754971660</v>
       </c>
       <c r="P6" t="n">
         <v>17950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>부정적인 재무 상태에도 불구하고 투자 심리 유지. LG 로봇 관련 테마 기대.</t>
+          <t>내년 및 후년 목표 주가 제시. 부채 상환 능력 및 LG 로봇 관련 재평가 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['적자', '부채', '로봇']</t>
+          <t>['목표주가', '부채상환', 'LG로봇']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H7" t="n">
         <v>9.609999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.77</v>
       </c>
       <c r="O7" t="n">
-        <v>77296060485</v>
+        <v>78491330390</v>
       </c>
       <c r="P7" t="n">
         <v>23550</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속으로 인한 주가 하락 우려. 주가 조작 의혹 제기.</t>
+          <t>기관 및 외인 매도세에 따른 주가 하락 우려. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외인', '매도']</t>
+          <t>['기관매도', '외인매도', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>283500</v>
+        <v>284250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G8" t="n">
-        <v>2577</v>
+        <v>2408</v>
       </c>
       <c r="H8" t="n">
         <v>46.55</v>
@@ -1162,7 +1162,7 @@
         <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1620627439750</v>
+        <v>1733619210000</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 선물 상승에 따른 기대감. 정치적 언급과 함께 30만원 돌파 기대.</t>
+          <t>이재명 관련 언급과 함께 30만원 및 35만원 목표가 제시. 배당 기대감 및 시가총액 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '배당', '선물']</t>
+          <t>['배당', '목표주가', '시가총액']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1865000</v>
+        <v>24500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.36%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>486</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>1490</v>
+        <v>60</v>
       </c>
       <c r="H9" t="n">
-        <v>50.15</v>
+        <v>1.68</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1840000</v>
+        <v>23950</v>
       </c>
       <c r="K9" t="n">
-        <v>1899000</v>
+        <v>24400</v>
       </c>
       <c r="L9" t="n">
-        <v>1900000</v>
+        <v>25700</v>
       </c>
       <c r="M9" t="n">
-        <v>1851000</v>
+        <v>23050</v>
       </c>
       <c r="N9" t="n">
-        <v>50.17</v>
+        <v>1.76</v>
       </c>
       <c r="O9" t="n">
-        <v>1740102596500</v>
+        <v>55814868975</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>333000</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>-28000</v>
+        <v>-37000</v>
       </c>
       <c r="S9" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시와의 격차에 따른 기대감. 200만원 돌파 시도 및 외인 매매 동향 주시.</t>
+          <t>미국 타임지 '세계 최고 헬스테크 기업' 선정 소식에 대한 기대감 존재. 추세선 상방 결정 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '외인', '200만원']</t>
+          <t>['헬스테크', '타임지', '추세선']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17970</v>
+        <v>3805</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.90%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.76</v>
+        <v>-0.35</v>
       </c>
       <c r="E10" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>426</v>
+        <v>149</v>
       </c>
       <c r="H10" t="n">
-        <v>5.46</v>
+        <v>0.61</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,28 +1331,28 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17810</v>
+        <v>3725</v>
       </c>
       <c r="K10" t="n">
-        <v>17950</v>
+        <v>3740</v>
       </c>
       <c r="L10" t="n">
-        <v>18180</v>
+        <v>4090</v>
       </c>
       <c r="M10" t="n">
-        <v>17410</v>
+        <v>3705</v>
       </c>
       <c r="N10" t="n">
-        <v>6.22</v>
+        <v>0.96</v>
       </c>
       <c r="O10" t="n">
-        <v>93595559240</v>
+        <v>21913875758</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>6300</v>
       </c>
       <c r="Q10" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R10" t="n">
         <v>-78000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2만원 돌파 기대감 표출과 함께 명절 전 주가 하락 가능성에 대한 언급.</t>
+          <t>주가 급락 후 매도세 강하게 나타남. 유상증자 가격 이하 분할 매수 의견 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주포', '명절', '거래량']</t>
+          <t>['주가', '매도세', '유증가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31150</v>
+        <v>1872000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.80%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.62</v>
+        <v>-0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>485</v>
       </c>
       <c r="G11" t="n">
-        <v>93</v>
+        <v>1548</v>
       </c>
       <c r="H11" t="n">
-        <v>52.81</v>
+        <v>50.15</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>31400</v>
+        <v>1840000</v>
       </c>
       <c r="K11" t="n">
-        <v>31500</v>
+        <v>1899000</v>
       </c>
       <c r="L11" t="n">
-        <v>32100</v>
+        <v>1900000</v>
       </c>
       <c r="M11" t="n">
-        <v>31100</v>
+        <v>1851000</v>
       </c>
       <c r="N11" t="n">
-        <v>25.75</v>
+        <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>57919728175</v>
+        <v>1859075493500</v>
       </c>
       <c r="P11" t="n">
-        <v>32100</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>21000</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>29000</v>
+        <v>-28000</v>
       </c>
       <c r="S11" t="n">
-        <v>9000</v>
+        <v>80000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망에 따른 주가 상승 기대. 합병 효과는 장기적.</t>
+          <t>미국 및 국내 시장 비교하며 국내 시장 부진 지적. 200만원대 안착 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '기대']</t>
+          <t>['미국시장', '국내시장', '200만원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30700</v>
+        <v>17860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>-0.76</v>
       </c>
       <c r="E12" t="n">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>959</v>
+        <v>440</v>
       </c>
       <c r="H12" t="n">
-        <v>16.63</v>
+        <v>5.46</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31050</v>
+        <v>17810</v>
       </c>
       <c r="K12" t="n">
-        <v>31300</v>
+        <v>17950</v>
       </c>
       <c r="L12" t="n">
-        <v>31550</v>
+        <v>18180</v>
       </c>
       <c r="M12" t="n">
-        <v>30450</v>
+        <v>17410</v>
       </c>
       <c r="N12" t="n">
-        <v>16.42</v>
+        <v>6.22</v>
       </c>
       <c r="O12" t="n">
-        <v>4578587425</v>
+        <v>96222732500</v>
       </c>
       <c r="P12" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-27000</v>
+        <v>-78000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 상승 및 간암/담관암 신약 FDA 승인 기대감, 과거 패턴 언급.</t>
+          <t>2만원 돌파 기대감 표출과 함께 명절 전 주가 하락 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신약', 'FDA', '승인']</t>
+          <t>['주포', '명절', '거래량']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23300</v>
+        <v>31250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.71%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.08</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="H13" t="n">
-        <v>1.68</v>
+        <v>52.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>23950</v>
+        <v>31400</v>
       </c>
       <c r="K13" t="n">
-        <v>24400</v>
+        <v>31500</v>
       </c>
       <c r="L13" t="n">
-        <v>25700</v>
+        <v>32100</v>
       </c>
       <c r="M13" t="n">
-        <v>23050</v>
+        <v>31100</v>
       </c>
       <c r="N13" t="n">
-        <v>1.76</v>
+        <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>51606891825</v>
+        <v>59726417775</v>
       </c>
       <c r="P13" t="n">
-        <v>39350</v>
+        <v>32100</v>
       </c>
       <c r="Q13" t="n">
-        <v>8200</v>
+        <v>21000</v>
       </c>
       <c r="R13" t="n">
-        <v>-37000</v>
+        <v>29000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>타임지 선정 '세계 최고 헬스테크 기업' 선정 사실 기반, 상장 기대감과 실망감 교차.</t>
+          <t>인천공항 이용객 증가 및 영업이익 전망. 합병 효과 및 외인 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '상장']</t>
+          <t>['영업이익', '합병효과', '외인매매']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83700</v>
+        <v>30650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="F14" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="G14" t="n">
-        <v>731</v>
+        <v>1015</v>
       </c>
       <c r="H14" t="n">
-        <v>23.03</v>
+        <v>16.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>86500</v>
+        <v>31050</v>
       </c>
       <c r="K14" t="n">
-        <v>86100</v>
+        <v>31300</v>
       </c>
       <c r="L14" t="n">
-        <v>86100</v>
+        <v>31550</v>
       </c>
       <c r="M14" t="n">
-        <v>83500</v>
+        <v>30450</v>
       </c>
       <c r="N14" t="n">
-        <v>23.05</v>
+        <v>16.42</v>
       </c>
       <c r="O14" t="n">
-        <v>91575594950</v>
+        <v>4797796675</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R14" t="n">
-        <v>-248000</v>
+        <v>-27000</v>
       </c>
       <c r="S14" t="n">
-        <v>-42000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전 관련 호재에도 불구하고 주가 하락 우려. 차트 붕괴 및 테마 소멸 가능성.</t>
+          <t>미국 릴레이테라퓨틱스 상승 및 간암/담관암 신약 FDA 승인 기대감, 과거 패턴 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '호재']</t>
+          <t>['신약', 'FDA', '승인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49350</v>
+        <v>83600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>66</v>
+        <v>254</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="G15" t="n">
-        <v>107</v>
+        <v>761</v>
       </c>
       <c r="H15" t="n">
-        <v>38.34</v>
+        <v>23.03</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51200</v>
+        <v>86500</v>
       </c>
       <c r="K15" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="L15" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="M15" t="n">
-        <v>48800</v>
+        <v>83500</v>
       </c>
       <c r="N15" t="n">
-        <v>38.44</v>
+        <v>23.05</v>
       </c>
       <c r="O15" t="n">
-        <v>48473800450</v>
+        <v>98649028350</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-182000</v>
+        <v>-248000</v>
       </c>
       <c r="S15" t="n">
-        <v>-21000</v>
+        <v>-42000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대규모 수주에도 불구하고 주가 하락 지속. IR 담당자의 주가 상승 관련 소통 부재.</t>
+          <t>미국 한국형 원전 수주 확정 및 SMR 기술 기대. 단기 하락 및 차트 붕괴 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '주가하락', 'IR']</t>
+          <t>['원전수주', 'SMR', '차트붕괴']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17720</v>
+        <v>49300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.74%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>295</v>
+        <v>109</v>
       </c>
       <c r="H16" t="n">
-        <v>10.38</v>
+        <v>38.34</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,58 +1883,150 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18800</v>
+        <v>51200</v>
       </c>
       <c r="K16" t="n">
-        <v>18800</v>
+        <v>51600</v>
       </c>
       <c r="L16" t="n">
-        <v>18800</v>
+        <v>51600</v>
       </c>
       <c r="M16" t="n">
-        <v>17600</v>
+        <v>48800</v>
       </c>
       <c r="N16" t="n">
-        <v>10.47</v>
+        <v>38.44</v>
       </c>
       <c r="O16" t="n">
-        <v>77394029805</v>
+        <v>50620645150</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R16" t="n">
-        <v>-1005000</v>
+        <v>-182000</v>
       </c>
       <c r="S16" t="n">
-        <v>-51000</v>
+        <v>-21000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 건설 및 원전 상승에 따른 기대감. 공매도 세력과의 갈등 및 대차 해지 운동.</t>
+          <t>대규모 수주에도 불구하고 주가 하락 지속. IR 담당자의 주가 상승 관련 소통 부재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '원전', '대차']</t>
+          <t>['수주', '주가하락', 'IR']</t>
         </is>
       </c>
       <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>17630</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-6.22%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E17" t="n">
+        <v>107</v>
+      </c>
+      <c r="F17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G17" t="n">
+        <v>320</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K17" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>17600</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O17" t="n">
+        <v>82779377350</v>
+      </c>
+      <c r="P17" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1005000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>대차 해지 운동 동참 호소 및 공매도 세력 파산 기대감. 원전 및 반도체 산업 관련 긍정적 전망.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['대차해지', '공매도', '원전']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
         <v>22</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20260923_10.xlsx
+++ b/data/trending_integrated_20260923_10.xlsx
@@ -578,10 +578,10 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
         <v>56</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31131132533</v>
+        <v>31168013468</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3연상 기록 및 AI 관련 기대감. 추가 상승 및 단기 폭락 가능성 언급.</t>
+          <t>3연상 기록하며 강한 상승세를 보였으나, 단기 급락 및 폭락 가능성 경고도 존재. 엔트로픽 관련 AI 테마 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['3연상', 'AI', '단기폭락']</t>
+          <t>['3연상', 'AI 테마', '급락 경고']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18730</v>
+        <v>18800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.24%</t>
+          <t>'+13.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>232050409745</v>
+        <v>239104174030</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 기대감. 공매도 세력에 대한 경계.</t>
+          <t>미국 양자 관련주 급등에 따른 기대감, 공매도 세력에 대한 경고 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '공매도', '아이온큐']</t>
+          <t>['양자보안', '공매도', '단타']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220000</v>
+        <v>3920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+5.23%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>-0.35</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>231</v>
+        <v>159</v>
       </c>
       <c r="H4" t="n">
-        <v>75.51000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>211500</v>
+        <v>3725</v>
       </c>
       <c r="K4" t="n">
-        <v>217000</v>
+        <v>3740</v>
       </c>
       <c r="L4" t="n">
-        <v>220000</v>
+        <v>4090</v>
       </c>
       <c r="M4" t="n">
-        <v>216500</v>
+        <v>3705</v>
       </c>
       <c r="N4" t="n">
-        <v>75.5</v>
+        <v>0.96</v>
       </c>
       <c r="O4" t="n">
-        <v>452791949000</v>
+        <v>26585105967</v>
       </c>
       <c r="P4" t="n">
-        <v>243500</v>
+        <v>6300</v>
       </c>
       <c r="Q4" t="n">
-        <v>65000</v>
+        <v>1738</v>
       </c>
       <c r="R4" t="n">
-        <v>276000</v>
+        <v>-78000</v>
       </c>
       <c r="S4" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>장기 보유 및 배당금 증액 기대. 특별 배당 및 소각 이슈 언급.</t>
+          <t>연이은 하락 후 주가 부양 시도 및 허매도 의혹 제기. 유증가 이하 분할 매수 의견 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['장기보유', '배당금', '특별배당']</t>
+          <t>['주포', '허매도', '유증가']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2995</v>
+        <v>3005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.81%</t>
+          <t>'+4.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.92</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>0.48</v>
       </c>
       <c r="O5" t="n">
-        <v>17958393641</v>
+        <v>18194626666</v>
       </c>
       <c r="P5" t="n">
         <v>4760</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유상증자 관련 논란 속 주가 반등 시도. 2분기 중간 분석 결과 발표 예정.</t>
+          <t>유상증자 결정 속에서 주가 변동성 확대. 중간 분석 결과 발표 예정 및 차트 흐름 주목.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유상증자', '주가', '분석']</t>
+          <t>['유상증자', '중간분석', '차트']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8740</v>
+        <v>8780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.19%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H6" t="n">
         <v>26.63</v>
@@ -978,7 +978,7 @@
         <v>26.58</v>
       </c>
       <c r="O6" t="n">
-        <v>12754971660</v>
+        <v>13366457905</v>
       </c>
       <c r="P6" t="n">
         <v>17950</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>내년 및 후년 목표 주가 제시. 부채 상환 능력 및 LG 로봇 관련 재평가 기대.</t>
+          <t>적자에도 불구하고 부채 상환 능력 및 향후 실적 개선에 대한 기대감, 10000원 돌파 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['목표주가', '부채상환', 'LG로봇']</t>
+          <t>['실적개선', '부채상환', '목표가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14000</v>
+        <v>219000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.94%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.16</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="H7" t="n">
-        <v>9.609999999999999</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13600</v>
+        <v>211500</v>
       </c>
       <c r="K7" t="n">
-        <v>13750</v>
+        <v>217000</v>
       </c>
       <c r="L7" t="n">
-        <v>15050</v>
+        <v>220000</v>
       </c>
       <c r="M7" t="n">
-        <v>13750</v>
+        <v>216500</v>
       </c>
       <c r="N7" t="n">
-        <v>9.77</v>
+        <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>78491330390</v>
+        <v>493874913000</v>
       </c>
       <c r="P7" t="n">
-        <v>23550</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>5780</v>
+        <v>65000</v>
       </c>
       <c r="R7" t="n">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="S7" t="n">
-        <v>-64000</v>
+        <v>-25000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세에 따른 주가 하락 우려. 주가 조작 의혹 제기.</t>
+          <t>장기 보유 및 배당금 증액에 대한 기대, 우선주 소각 및 30만원 돌파 목표 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관매도', '외인매도', '주가조작']</t>
+          <t>['배당', '우선주', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>284250</v>
+        <v>13990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+2.87%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>458</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>2408</v>
+        <v>150</v>
       </c>
       <c r="H8" t="n">
-        <v>46.55</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>276500</v>
+        <v>13600</v>
       </c>
       <c r="K8" t="n">
-        <v>284500</v>
+        <v>13750</v>
       </c>
       <c r="L8" t="n">
-        <v>285000</v>
+        <v>15050</v>
       </c>
       <c r="M8" t="n">
-        <v>282500</v>
+        <v>13750</v>
       </c>
       <c r="N8" t="n">
-        <v>46.56</v>
+        <v>9.77</v>
       </c>
       <c r="O8" t="n">
-        <v>1733619210000</v>
+        <v>79544842305</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>23550</v>
       </c>
       <c r="Q8" t="n">
-        <v>82400</v>
+        <v>5780</v>
       </c>
       <c r="R8" t="n">
-        <v>1308000</v>
+        <v>275000</v>
       </c>
       <c r="S8" t="n">
-        <v>346000</v>
+        <v>-64000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 관련 언급과 함께 30만원 및 35만원 목표가 제시. 배당 기대감 및 시가총액 상승 전망.</t>
+          <t>기관 및 외인 매도세와 주가 하락에 대한 불만, 도박성 언급이 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '시가총액']</t>
+          <t>['기관', '외인', '하락']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24500</v>
+        <v>283500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>455</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>2360</v>
       </c>
       <c r="H9" t="n">
-        <v>1.68</v>
+        <v>46.55</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>23950</v>
+        <v>276500</v>
       </c>
       <c r="K9" t="n">
-        <v>24400</v>
+        <v>284500</v>
       </c>
       <c r="L9" t="n">
-        <v>25700</v>
+        <v>285000</v>
       </c>
       <c r="M9" t="n">
-        <v>23050</v>
+        <v>282500</v>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>46.56</v>
       </c>
       <c r="O9" t="n">
-        <v>55814868975</v>
+        <v>1850601181500</v>
       </c>
       <c r="P9" t="n">
-        <v>39350</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>8200</v>
+        <v>82400</v>
       </c>
       <c r="R9" t="n">
-        <v>-37000</v>
+        <v>1308000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 타임지 '세계 최고 헬스테크 기업' 선정 소식에 대한 기대감 존재. 추세선 상방 결정 가능성 언급.</t>
+          <t>이재명 관련 정치적 언급과 함께 연말 배당 및 29만원 돌파 기대감이 있으나, 35만원 및 57만 목표가는 근거 부족.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '추세선']</t>
+          <t>['배당', '목표주가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3805</v>
+        <v>1865000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+1.36%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.35</v>
+        <v>-0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>488</v>
       </c>
       <c r="G10" t="n">
-        <v>149</v>
+        <v>1586</v>
       </c>
       <c r="H10" t="n">
-        <v>0.61</v>
+        <v>50.15</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3725</v>
+        <v>1840000</v>
       </c>
       <c r="K10" t="n">
-        <v>3740</v>
+        <v>1899000</v>
       </c>
       <c r="L10" t="n">
-        <v>4090</v>
+        <v>1900000</v>
       </c>
       <c r="M10" t="n">
-        <v>3705</v>
+        <v>1851000</v>
       </c>
       <c r="N10" t="n">
-        <v>0.96</v>
+        <v>50.17</v>
       </c>
       <c r="O10" t="n">
-        <v>21913875758</v>
+        <v>1957757363000</v>
       </c>
       <c r="P10" t="n">
-        <v>6300</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1738</v>
+        <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>-78000</v>
+        <v>-28000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 급락 후 매도세 강하게 나타남. 유상증자 가격 이하 분할 매수 의견 존재.</t>
+          <t>한국 주식 시장에 대한 불신과 미국 시장과의 괴리감, 외인 매도세에 대한 관망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가', '매도세', '유증가']</t>
+          <t>['미국시장', '괴리율', '외인매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1872000</v>
+        <v>17820</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.02</v>
+        <v>-0.76</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
-        <v>485</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>1548</v>
+        <v>478</v>
       </c>
       <c r="H11" t="n">
-        <v>50.15</v>
+        <v>5.46</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1840000</v>
+        <v>17810</v>
       </c>
       <c r="K11" t="n">
-        <v>1899000</v>
+        <v>17950</v>
       </c>
       <c r="L11" t="n">
-        <v>1900000</v>
+        <v>18180</v>
       </c>
       <c r="M11" t="n">
-        <v>1851000</v>
+        <v>17410</v>
       </c>
       <c r="N11" t="n">
-        <v>50.17</v>
+        <v>6.22</v>
       </c>
       <c r="O11" t="n">
-        <v>1859075493500</v>
+        <v>98632813685</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>333000</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-28000</v>
+        <v>-78000</v>
       </c>
       <c r="S11" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 및 국내 시장 비교하며 국내 시장 부진 지적. 200만원대 안착 기대.</t>
+          <t>연휴 전 상승 기대감 속에서 2만원 돌파 시도. 쇼티지 현상 및 광통신 섹터 흐름 긍정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미국시장', '국내시장', '200만원']</t>
+          <t>['연휴 기대', '쇼티지', '광통신']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17860</v>
+        <v>31250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.76</v>
+        <v>0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>440</v>
+        <v>99</v>
       </c>
       <c r="H12" t="n">
-        <v>5.46</v>
+        <v>52.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17810</v>
+        <v>31400</v>
       </c>
       <c r="K12" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="L12" t="n">
-        <v>18180</v>
+        <v>32100</v>
       </c>
       <c r="M12" t="n">
-        <v>17410</v>
+        <v>31100</v>
       </c>
       <c r="N12" t="n">
-        <v>6.22</v>
+        <v>25.75</v>
       </c>
       <c r="O12" t="n">
-        <v>96222732500</v>
+        <v>61883720550</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>32100</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>21000</v>
       </c>
       <c r="R12" t="n">
-        <v>-78000</v>
+        <v>29000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2만원 돌파 기대감 표출과 함께 명절 전 주가 하락 가능성에 대한 언급.</t>
+          <t>내년 영업이익 전망 언급에도 불구하고, 주가 하락 및 단기 차익 실현에 대한 부정적 의견이 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주포', '명절', '거래량']</t>
+          <t>['영업이익', '합병효과']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31250</v>
+        <v>23800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'-0.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="H13" t="n">
-        <v>52.81</v>
+        <v>1.68</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>31400</v>
+        <v>23950</v>
       </c>
       <c r="K13" t="n">
-        <v>31500</v>
+        <v>24400</v>
       </c>
       <c r="L13" t="n">
-        <v>32100</v>
+        <v>25700</v>
       </c>
       <c r="M13" t="n">
-        <v>31100</v>
+        <v>23050</v>
       </c>
       <c r="N13" t="n">
-        <v>25.75</v>
+        <v>1.76</v>
       </c>
       <c r="O13" t="n">
-        <v>59726417775</v>
+        <v>60965527950</v>
       </c>
       <c r="P13" t="n">
-        <v>32100</v>
+        <v>39350</v>
       </c>
       <c r="Q13" t="n">
-        <v>21000</v>
+        <v>8200</v>
       </c>
       <c r="R13" t="n">
-        <v>29000</v>
+        <v>-37000</v>
       </c>
       <c r="S13" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 영업이익 전망. 합병 효과 및 외인 매매 동향 주시.</t>
+          <t>타임지 선정 '세계 최고 헬스테크 기업' 소식에 따른 주가 상승 기대. 추세선 상방 돌파 여부 주목.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '합병효과', '외인매매']</t>
+          <t>['헬스테크', '타임지', '추세선']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30650</v>
+        <v>30600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F14" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G14" t="n">
-        <v>1015</v>
+        <v>1071</v>
       </c>
       <c r="H14" t="n">
         <v>16.63</v>
@@ -1714,7 +1714,7 @@
         <v>16.42</v>
       </c>
       <c r="O14" t="n">
-        <v>4797796675</v>
+        <v>4954916175</v>
       </c>
       <c r="P14" t="n">
         <v>69200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 상승 및 간암/담관암 신약 FDA 승인 기대감, 과거 패턴 언급.</t>
+          <t>간암 및 담관암 신약 FDA 허가 기대감 고조. 릴레이테라퓨틱스 상승 및 HLB 그룹주 동반 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신약', 'FDA', '승인']</t>
+          <t>['FDA 허가', '리보세라닙', '신약개발']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83600</v>
+        <v>83100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.35%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="F15" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G15" t="n">
-        <v>761</v>
+        <v>864</v>
       </c>
       <c r="H15" t="n">
         <v>23.03</v>
@@ -1800,13 +1800,13 @@
         <v>86100</v>
       </c>
       <c r="M15" t="n">
-        <v>83500</v>
+        <v>83100</v>
       </c>
       <c r="N15" t="n">
         <v>23.05</v>
       </c>
       <c r="O15" t="n">
-        <v>98649028350</v>
+        <v>108857669600</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 한국형 원전 수주 확정 및 SMR 기술 기대. 단기 하락 및 차트 붕괴 우려.</t>
+          <t>미국 원전 수주 관련 호재에도 불구하고, 주가 하락 및 차트 붕괴에 대한 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전수주', 'SMR', '차트붕괴']</t>
+          <t>['원전', '수주', '차트']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49300</v>
+        <v>49100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-4.10%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H16" t="n">
         <v>38.34</v>
@@ -1898,7 +1898,7 @@
         <v>38.44</v>
       </c>
       <c r="O16" t="n">
-        <v>50620645150</v>
+        <v>52247989300</v>
       </c>
       <c r="P16" t="n">
         <v>67300</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대규모 수주에도 불구하고 주가 하락 지속. IR 담당자의 주가 상승 관련 소통 부재.</t>
+          <t>주가 하락 및 20일선 지지 실패에 대한 실망감, 6개월 보유에 대한 자조적 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '주가하락', 'IR']</t>
+          <t>['주가하락', '20일선']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17630</v>
+        <v>17570</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.22%</t>
+          <t>'-6.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G17" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="H17" t="n">
         <v>10.38</v>
@@ -1984,13 +1984,13 @@
         <v>18800</v>
       </c>
       <c r="M17" t="n">
-        <v>17600</v>
+        <v>17560</v>
       </c>
       <c r="N17" t="n">
         <v>10.47</v>
       </c>
       <c r="O17" t="n">
-        <v>82779377350</v>
+        <v>89473412115</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차 해지 운동 동참 호소 및 공매도 세력 파산 기대감. 원전 및 반도체 산업 관련 긍정적 전망.</t>
+          <t>공매도 세력 파산 및 대차 해지 운동에 대한 기대감, 원전 관련 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '원전']</t>
+          <t>['공매도', '대차해지', '원전']</t>
         </is>
       </c>
       <c r="X17" t="n">

--- a/data/trending_integrated_20260923_10.xlsx
+++ b/data/trending_integrated_20260923_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
         <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31168013468</v>
+        <v>31199861858</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18800</v>
+        <v>18400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.66%</t>
+          <t>'+18.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="H3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16540</v>
+        <v>15520</v>
       </c>
       <c r="K3" t="n">
-        <v>17530</v>
+        <v>15800</v>
       </c>
       <c r="L3" t="n">
-        <v>19950</v>
+        <v>19050</v>
       </c>
       <c r="M3" t="n">
-        <v>17500</v>
+        <v>15200</v>
       </c>
       <c r="N3" t="n">
-        <v>0.77</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>239104174030</v>
+        <v>49073176250</v>
       </c>
       <c r="P3" t="n">
-        <v>30550</v>
+        <v>34650</v>
       </c>
       <c r="Q3" t="n">
-        <v>6100</v>
+        <v>6980</v>
       </c>
       <c r="R3" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 기대감, 공매도 세력에 대한 경고 및 단기 급등 가능성 언급.</t>
+          <t>NASA 우주 임무 적합 장비 선정 및 119 필수 공급 등 호재 부각. 스페이스X 탑재 확정 및 기술력 검증.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '공매도', '단타']</t>
+          <t>['스페이스X', 'NASA', '엑스레이 발생기']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3920</v>
+        <v>14990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.23%</t>
+          <t>'+15.31%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.35</v>
+        <v>0.42</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3725</v>
+        <v>13000</v>
       </c>
       <c r="K4" t="n">
-        <v>3740</v>
+        <v>12870</v>
       </c>
       <c r="L4" t="n">
-        <v>4090</v>
+        <v>15900</v>
       </c>
       <c r="M4" t="n">
-        <v>3705</v>
+        <v>12650</v>
       </c>
       <c r="N4" t="n">
-        <v>0.96</v>
+        <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>26585105967</v>
+        <v>113429532730</v>
       </c>
       <c r="P4" t="n">
-        <v>6300</v>
+        <v>25700</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>4600</v>
       </c>
       <c r="R4" t="n">
-        <v>-78000</v>
+        <v>95000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>연이은 하락 후 주가 부양 시도 및 허매도 의혹 제기. 유증가 이하 분할 매수 의견 제시.</t>
+          <t>추석 명절 앞두고 상승 기대감 있으나, 단기 과열 지정 우려 및 계단식 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '허매도', '유증가']</t>
+          <t>['대상승', '단기과열', '계단식 하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3005</v>
+        <v>18790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.16%</t>
+          <t>'+13.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.92</v>
+        <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2885</v>
+        <v>16540</v>
       </c>
       <c r="K5" t="n">
-        <v>3000</v>
+        <v>17530</v>
       </c>
       <c r="L5" t="n">
-        <v>3480</v>
+        <v>19950</v>
       </c>
       <c r="M5" t="n">
-        <v>2885</v>
+        <v>17500</v>
       </c>
       <c r="N5" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>18194626666</v>
+        <v>243061775950</v>
       </c>
       <c r="P5" t="n">
-        <v>4760</v>
+        <v>30550</v>
       </c>
       <c r="Q5" t="n">
-        <v>973</v>
+        <v>6100</v>
       </c>
       <c r="R5" t="n">
-        <v>-235000</v>
+        <v>118000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유상증자 결정 속에서 주가 변동성 확대. 중간 분석 결과 발표 예정 및 차트 흐름 주목.</t>
+          <t>미국 양자 관련주 급등에 따른 국내 양자보안주 동반 상승 기대, 공매도 세력에 대한 경계.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유상증자', '중간분석', '차트']</t>
+          <t>['양자 보안', '아이온큐', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8780</v>
+        <v>4110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.66%</t>
+          <t>'+10.34%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>-0.35</v>
       </c>
       <c r="E6" t="n">
         <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H6" t="n">
-        <v>26.63</v>
+        <v>0.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8470</v>
+        <v>3725</v>
       </c>
       <c r="K6" t="n">
-        <v>8510</v>
+        <v>3740</v>
       </c>
       <c r="L6" t="n">
-        <v>8870</v>
+        <v>4110</v>
       </c>
       <c r="M6" t="n">
-        <v>8480</v>
+        <v>3705</v>
       </c>
       <c r="N6" t="n">
-        <v>26.58</v>
+        <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>13366457905</v>
+        <v>30859187536</v>
       </c>
       <c r="P6" t="n">
-        <v>17950</v>
+        <v>6300</v>
       </c>
       <c r="Q6" t="n">
-        <v>8120</v>
+        <v>1738</v>
       </c>
       <c r="R6" t="n">
-        <v>359000</v>
+        <v>-78000</v>
       </c>
       <c r="S6" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>적자에도 불구하고 부채 상환 능력 및 향후 실적 개선에 대한 기대감, 10000원 돌파 전망.</t>
+          <t>급락세 속 물량 떠넘기기 및 공매도 의혹 제기. 유증가 이하 분할 매수 의견 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적개선', '부채상환', '목표가']</t>
+          <t>['주포', '공매도', '유증가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>219000</v>
+        <v>3000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+3.99%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.92</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>239</v>
+        <v>123</v>
       </c>
       <c r="H7" t="n">
-        <v>75.51000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>211500</v>
+        <v>2885</v>
       </c>
       <c r="K7" t="n">
-        <v>217000</v>
+        <v>3000</v>
       </c>
       <c r="L7" t="n">
-        <v>220000</v>
+        <v>3480</v>
       </c>
       <c r="M7" t="n">
-        <v>216500</v>
+        <v>2885</v>
       </c>
       <c r="N7" t="n">
-        <v>75.5</v>
+        <v>0.48</v>
       </c>
       <c r="O7" t="n">
-        <v>493874913000</v>
+        <v>18404808242</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>4760</v>
       </c>
       <c r="Q7" t="n">
-        <v>65000</v>
+        <v>973</v>
       </c>
       <c r="R7" t="n">
-        <v>276000</v>
+        <v>-235000</v>
       </c>
       <c r="S7" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>장기 보유 및 배당금 증액에 대한 기대, 우선주 소각 및 30만원 돌파 목표 언급.</t>
+          <t>유상증자 결정 속에서 주가 변동성 확대. 중간 분석 결과 발표 예정 및 차트 흐름 주목.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['배당', '우선주', '목표가']</t>
+          <t>['유상증자', '중간분석', '차트']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13990</v>
+        <v>219000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.87%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.16</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H8" t="n">
-        <v>9.609999999999999</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13600</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>13750</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>15050</v>
+        <v>220000</v>
       </c>
       <c r="M8" t="n">
-        <v>13750</v>
+        <v>216500</v>
       </c>
       <c r="N8" t="n">
-        <v>9.77</v>
+        <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>79544842305</v>
+        <v>521752799000</v>
       </c>
       <c r="P8" t="n">
-        <v>23550</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>5780</v>
+        <v>65000</v>
       </c>
       <c r="R8" t="n">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="S8" t="n">
-        <v>-64000</v>
+        <v>-25000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세와 주가 하락에 대한 불만, 도박성 언급이 다수.</t>
+          <t>장기 보유 및 높은 배당금 기대, JP모건의 목표가 30만원 제시, 외국인 매수에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기관', '외인', '하락']</t>
+          <t>['배당', '우선주', 'JP모건']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>283500</v>
+        <v>8740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+3.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>455</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>2360</v>
+        <v>179</v>
       </c>
       <c r="H9" t="n">
-        <v>46.55</v>
+        <v>26.63</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>276500</v>
+        <v>8470</v>
       </c>
       <c r="K9" t="n">
-        <v>284500</v>
+        <v>8510</v>
       </c>
       <c r="L9" t="n">
-        <v>285000</v>
+        <v>8870</v>
       </c>
       <c r="M9" t="n">
-        <v>282500</v>
+        <v>8480</v>
       </c>
       <c r="N9" t="n">
-        <v>46.56</v>
+        <v>26.58</v>
       </c>
       <c r="O9" t="n">
-        <v>1850601181500</v>
+        <v>13998859435</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>82400</v>
+        <v>8120</v>
       </c>
       <c r="R9" t="n">
-        <v>1308000</v>
+        <v>359000</v>
       </c>
       <c r="S9" t="n">
-        <v>346000</v>
+        <v>23000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 관련 정치적 언급과 함께 연말 배당 및 29만원 돌파 기대감이 있으나, 35만원 및 57만 목표가는 근거 부족.</t>
+          <t>유리 인터포저 및 유리기판 사업의 구조적 차별화 언급, 부채 상환 부담 및 적자 구조에 대한 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['배당', '목표주가']</t>
+          <t>['유리 인터포저', '유리기판', '부채']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1865000</v>
+        <v>13900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.36%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>488</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>1586</v>
+        <v>153</v>
       </c>
       <c r="H10" t="n">
-        <v>50.15</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1840000</v>
+        <v>13600</v>
       </c>
       <c r="K10" t="n">
-        <v>1899000</v>
+        <v>13750</v>
       </c>
       <c r="L10" t="n">
-        <v>1900000</v>
+        <v>15050</v>
       </c>
       <c r="M10" t="n">
-        <v>1851000</v>
+        <v>13750</v>
       </c>
       <c r="N10" t="n">
-        <v>50.17</v>
+        <v>9.77</v>
       </c>
       <c r="O10" t="n">
-        <v>1957757363000</v>
+        <v>81711239380</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>23550</v>
       </c>
       <c r="Q10" t="n">
-        <v>333000</v>
+        <v>5780</v>
       </c>
       <c r="R10" t="n">
-        <v>-28000</v>
+        <v>275000</v>
       </c>
       <c r="S10" t="n">
-        <v>80000</v>
+        <v>-64000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>한국 주식 시장에 대한 불신과 미국 시장과의 괴리감, 외인 매도세에 대한 관망.</t>
+          <t>기관 및 외인 매도세와 주가 하락에 대한 불만, 도박성 언급이 다수.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미국시장', '괴리율', '외인매도']</t>
+          <t>['기관', '외인', '하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17820</v>
+        <v>282500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+2.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.76</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>456</v>
       </c>
       <c r="G11" t="n">
-        <v>478</v>
+        <v>2264</v>
       </c>
       <c r="H11" t="n">
-        <v>5.46</v>
+        <v>46.55</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17810</v>
+        <v>276500</v>
       </c>
       <c r="K11" t="n">
-        <v>17950</v>
+        <v>284500</v>
       </c>
       <c r="L11" t="n">
-        <v>18180</v>
+        <v>285000</v>
       </c>
       <c r="M11" t="n">
-        <v>17410</v>
+        <v>282500</v>
       </c>
       <c r="N11" t="n">
-        <v>6.22</v>
+        <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>98632813685</v>
+        <v>1940482570250</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>82400</v>
       </c>
       <c r="R11" t="n">
-        <v>-78000</v>
+        <v>1308000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>연휴 전 상승 기대감 속에서 2만원 돌파 시도. 쇼티지 현상 및 광통신 섹터 흐름 긍정적 전망.</t>
+          <t>이재명 대통령 언급과 함께 35만원 목표 제시, JP모건의 HBM 1위 인정 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['연휴 기대', '쇼티지', '광통신']</t>
+          <t>['HBM', 'JP모건', '배당']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31250</v>
+        <v>1857000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>495</v>
       </c>
       <c r="G12" t="n">
-        <v>99</v>
+        <v>1582</v>
       </c>
       <c r="H12" t="n">
-        <v>52.8</v>
+        <v>50.15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31400</v>
+        <v>1840000</v>
       </c>
       <c r="K12" t="n">
-        <v>31500</v>
+        <v>1899000</v>
       </c>
       <c r="L12" t="n">
-        <v>32100</v>
+        <v>1900000</v>
       </c>
       <c r="M12" t="n">
-        <v>31100</v>
+        <v>1851000</v>
       </c>
       <c r="N12" t="n">
-        <v>25.75</v>
+        <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>61883720550</v>
+        <v>2067601378500</v>
       </c>
       <c r="P12" t="n">
-        <v>32100</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>21000</v>
+        <v>333000</v>
       </c>
       <c r="R12" t="n">
-        <v>29000</v>
+        <v>-28000</v>
       </c>
       <c r="S12" t="n">
-        <v>9000</v>
+        <v>80000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>내년 영업이익 전망 언급에도 불구하고, 주가 하락 및 단기 차익 실현에 대한 부정적 의견이 존재.</t>
+          <t>미국 반도체주와의 괴리율 언급하며 국내 증시 부진 지적, 200만원대 돌파 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '합병효과']</t>
+          <t>['HBM', '반도체', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23800</v>
+        <v>17770</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.63%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.08</v>
+        <v>-0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>76</v>
+        <v>542</v>
       </c>
       <c r="H13" t="n">
-        <v>1.68</v>
+        <v>5.46</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>23950</v>
+        <v>17810</v>
       </c>
       <c r="K13" t="n">
-        <v>24400</v>
+        <v>17950</v>
       </c>
       <c r="L13" t="n">
-        <v>25700</v>
+        <v>18180</v>
       </c>
       <c r="M13" t="n">
-        <v>23050</v>
+        <v>17410</v>
       </c>
       <c r="N13" t="n">
-        <v>1.76</v>
+        <v>6.22</v>
       </c>
       <c r="O13" t="n">
-        <v>60965527950</v>
+        <v>101752394045</v>
       </c>
       <c r="P13" t="n">
-        <v>39350</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>8200</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>-37000</v>
+        <v>-78000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>타임지 선정 '세계 최고 헬스테크 기업' 소식에 따른 주가 상승 기대. 추세선 상방 돌파 여부 주목.</t>
+          <t>추석 연휴 전 2만원 돌파 기대감 속 쇼티지 및 주포 매집 정황 언급. 단기 과열 경고 가능성 배제.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '추세선']</t>
+          <t>['쇼티지', '주포', '단기 과열']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30600</v>
+        <v>31250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>1071</v>
+        <v>111</v>
       </c>
       <c r="H14" t="n">
-        <v>16.63</v>
+        <v>52.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31050</v>
+        <v>31400</v>
       </c>
       <c r="K14" t="n">
-        <v>31300</v>
+        <v>31500</v>
       </c>
       <c r="L14" t="n">
-        <v>31550</v>
+        <v>32100</v>
       </c>
       <c r="M14" t="n">
-        <v>30450</v>
+        <v>31100</v>
       </c>
       <c r="N14" t="n">
-        <v>16.42</v>
+        <v>25.75</v>
       </c>
       <c r="O14" t="n">
-        <v>4954916175</v>
+        <v>64907419525</v>
       </c>
       <c r="P14" t="n">
-        <v>69200</v>
+        <v>32100</v>
       </c>
       <c r="Q14" t="n">
-        <v>24150</v>
+        <v>21000</v>
       </c>
       <c r="R14" t="n">
-        <v>-27000</v>
+        <v>29000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>간암 및 담관암 신약 FDA 허가 기대감 고조. 릴레이테라퓨틱스 상승 및 HLB 그룹주 동반 상승 전망.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['FDA 허가', '리보세라닙', '신약개발']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83100</v>
+        <v>31250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>271</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>864</v>
+        <v>77</v>
       </c>
       <c r="H15" t="n">
-        <v>23.03</v>
+        <v>11.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>86500</v>
+        <v>31600</v>
       </c>
       <c r="K15" t="n">
-        <v>86100</v>
+        <v>32150</v>
       </c>
       <c r="L15" t="n">
-        <v>86100</v>
+        <v>32200</v>
       </c>
       <c r="M15" t="n">
-        <v>83100</v>
+        <v>30950</v>
       </c>
       <c r="N15" t="n">
-        <v>23.05</v>
+        <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>108857669600</v>
+        <v>44360747300</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>75900</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>15000</v>
       </c>
       <c r="R15" t="n">
-        <v>-248000</v>
+        <v>-295000</v>
       </c>
       <c r="S15" t="n">
-        <v>-42000</v>
+        <v>-29000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전 수주 관련 호재에도 불구하고, 주가 하락 및 차트 붕괴에 대한 우려.</t>
+          <t>구리 선물가 및 필지수 상승에 따른 기대감, LS마린과의 비교 및 가온전선과의 주가 흐름 차이 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '수주', '차트']</t>
+          <t>['구리', 'LS마린', '가온전선']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49100</v>
+        <v>30350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.10%</t>
+          <t>'-2.25%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1</v>
+        <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="G16" t="n">
-        <v>121</v>
+        <v>1136</v>
       </c>
       <c r="H16" t="n">
-        <v>38.34</v>
+        <v>16.63</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>51200</v>
+        <v>31050</v>
       </c>
       <c r="K16" t="n">
-        <v>51600</v>
+        <v>31300</v>
       </c>
       <c r="L16" t="n">
-        <v>51600</v>
+        <v>31550</v>
       </c>
       <c r="M16" t="n">
-        <v>48800</v>
+        <v>30350</v>
       </c>
       <c r="N16" t="n">
-        <v>38.44</v>
+        <v>16.42</v>
       </c>
       <c r="O16" t="n">
-        <v>52247989300</v>
+        <v>5431805725</v>
       </c>
       <c r="P16" t="n">
-        <v>67300</v>
+        <v>69200</v>
       </c>
       <c r="Q16" t="n">
-        <v>23150</v>
+        <v>24150</v>
       </c>
       <c r="R16" t="n">
-        <v>-182000</v>
+        <v>-27000</v>
       </c>
       <c r="S16" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 하락 및 20일선 지지 실패에 대한 실망감, 6개월 보유에 대한 자조적 언급.</t>
+          <t>간암 및 담관암 신약 FDA 허가 기대감 고조. 릴레이테라퓨틱스 상승 및 HLB 그룹주 동반 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가하락', '20일선']</t>
+          <t>['FDA 허가', '리보세라닙', '신약개발']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,97 +1936,373 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17570</v>
+        <v>23400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-2.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="H17" t="n">
-        <v>10.38</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18800</v>
+        <v>23950</v>
       </c>
       <c r="K17" t="n">
-        <v>18800</v>
+        <v>24400</v>
       </c>
       <c r="L17" t="n">
-        <v>18800</v>
+        <v>25700</v>
       </c>
       <c r="M17" t="n">
-        <v>17560</v>
+        <v>23050</v>
       </c>
       <c r="N17" t="n">
-        <v>10.47</v>
+        <v>1.76</v>
       </c>
       <c r="O17" t="n">
-        <v>89473412115</v>
+        <v>62487127150</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>39350</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>8200</v>
       </c>
       <c r="R17" t="n">
-        <v>-1005000</v>
+        <v>-37000</v>
       </c>
       <c r="S17" t="n">
-        <v>-51000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 세력 파산 및 대차 해지 운동에 대한 기대감, 원전 관련 긍정적 전망 언급.</t>
+          <t>타임지 세계 최고 헬스테크 기업 선정에도 불구하고 주가 변동성 및 프로그램 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '원전']</t>
+          <t>['헬스테크', '타임지', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>82800</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-4.28%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E18" t="n">
+        <v>308</v>
+      </c>
+      <c r="F18" t="n">
+        <v>181</v>
+      </c>
+      <c r="G18" t="n">
+        <v>930</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>86500</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86100</v>
+      </c>
+      <c r="L18" t="n">
+        <v>86100</v>
+      </c>
+      <c r="M18" t="n">
+        <v>82600</v>
+      </c>
+      <c r="N18" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="O18" t="n">
+        <v>123451353900</v>
+      </c>
+      <c r="P18" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-248000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-42000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>미국 한국형 원전 2기 수주 확정 소식에도 불구하고 주가 하락세, 투자자들의 불만 제기.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['원전', 'SMR', '수주']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>48950</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-4.39%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>75</v>
+      </c>
+      <c r="F19" t="n">
+        <v>47</v>
+      </c>
+      <c r="G19" t="n">
+        <v>127</v>
+      </c>
+      <c r="H19" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>51200</v>
+      </c>
+      <c r="K19" t="n">
+        <v>51600</v>
+      </c>
+      <c r="L19" t="n">
+        <v>51600</v>
+      </c>
+      <c r="M19" t="n">
+        <v>48800</v>
+      </c>
+      <c r="N19" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>54700767850</v>
+      </c>
+      <c r="P19" t="n">
+        <v>67300</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23150</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-182000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-21000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>20일선 지지 여부에 대한 기대와 실망 반복, 주가 박스권 내에서의 움직임에 대한 답답함 토로.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['20일선', '박스권', '조정']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>17480</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-7.02%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E20" t="n">
+        <v>138</v>
+      </c>
+      <c r="F20" t="n">
+        <v>83</v>
+      </c>
+      <c r="G20" t="n">
+        <v>424</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K20" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M20" t="n">
+        <v>17420</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O20" t="n">
+        <v>97540249910</v>
+      </c>
+      <c r="P20" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1005000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>공매도 세력 파산 언급과 함께 대차 해지 운동 촉구, 원전 관련 긍정적 전망.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['공매도', '대차 해지', '원전']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
         <v>22</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20260923_10.xlsx
+++ b/data/trending_integrated_20260923_10.xlsx
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31199861858</v>
+        <v>31212053618</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3연상 기록하며 강한 상승세를 보였으나, 단기 급락 및 폭락 가능성 경고도 존재. 엔트로픽 관련 AI 테마 언급.</t>
+          <t>3연상 기록, 엔트로픽 의료AI 관련 기대감 있으나 급락 가능성 언급. 개인 투자자 위주 거래.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['3연상', 'AI 테마', '급락 경고']</t>
+          <t>['3연상', '의료AI', '개인매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18400</v>
+        <v>18300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.56%</t>
+          <t>'+17.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>49073176250</v>
+        <v>52400550725</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NASA 우주 임무 적합 장비 선정 및 119 필수 공급 등 호재 부각. 스페이스X 탑재 확정 및 기술력 검증.</t>
+          <t>NASA, 레메디 초소형 엑스레이 발생기 'Xcam6' 우주 임무 적합 장비 선정. 스페이스X 탑재 관련 호재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['스페이스X', 'NASA', '엑스레이 발생기']</t>
+          <t>['NASA', '엑스레이', '스페이스X']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14990</v>
+        <v>19040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.31%</t>
+          <t>'+15.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.42</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="H4" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13000</v>
+        <v>16540</v>
       </c>
       <c r="K4" t="n">
-        <v>12870</v>
+        <v>17530</v>
       </c>
       <c r="L4" t="n">
-        <v>15900</v>
+        <v>19950</v>
       </c>
       <c r="M4" t="n">
-        <v>12650</v>
+        <v>17500</v>
       </c>
       <c r="N4" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>113429532730</v>
+        <v>247740860600</v>
       </c>
       <c r="P4" t="n">
-        <v>25700</v>
+        <v>30550</v>
       </c>
       <c r="Q4" t="n">
-        <v>4600</v>
+        <v>6100</v>
       </c>
       <c r="R4" t="n">
-        <v>95000</v>
+        <v>118000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>추석 명절 앞두고 상승 기대감 있으나, 단기 과열 지정 우려 및 계단식 하락 가능성 언급.</t>
+          <t>미국 양자 관련주 급등에 따른 국내 양자 보안주 상승 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대상승', '단기과열', '계단식 하락']</t>
+          <t>['양자보안', '아이온큐', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18790</v>
+        <v>14570</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.60%</t>
+          <t>'+12.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>204</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16540</v>
+        <v>13000</v>
       </c>
       <c r="K5" t="n">
-        <v>17530</v>
+        <v>12870</v>
       </c>
       <c r="L5" t="n">
-        <v>19950</v>
+        <v>15900</v>
       </c>
       <c r="M5" t="n">
-        <v>17500</v>
+        <v>12650</v>
       </c>
       <c r="N5" t="n">
-        <v>0.77</v>
+        <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>243061775950</v>
+        <v>117387710330</v>
       </c>
       <c r="P5" t="n">
-        <v>30550</v>
+        <v>25700</v>
       </c>
       <c r="Q5" t="n">
-        <v>6100</v>
+        <v>4600</v>
       </c>
       <c r="R5" t="n">
-        <v>118000</v>
+        <v>95000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 국내 양자보안주 동반 상승 기대, 공매도 세력에 대한 경계.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자 보안', '아이온큐', '공매도']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4110</v>
+        <v>4080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.34%</t>
+          <t>'+9.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.35</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H6" t="n">
         <v>0.61</v>
@@ -969,7 +969,7 @@
         <v>3740</v>
       </c>
       <c r="L6" t="n">
-        <v>4110</v>
+        <v>4200</v>
       </c>
       <c r="M6" t="n">
         <v>3705</v>
@@ -978,7 +978,7 @@
         <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>30859187536</v>
+        <v>45924343613</v>
       </c>
       <c r="P6" t="n">
         <v>6300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>급락세 속 물량 떠넘기기 및 공매도 의혹 제기. 유증가 이하 분할 매수 의견 제시.</t>
+          <t>주가 급락 및 대규모 거래량 발생, 유증 관련 정보 공유.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주포', '공매도', '유증가']</t>
+          <t>['유증', '도깨비', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3000</v>
+        <v>218500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.99%</t>
+          <t>'+3.31%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.92</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>123</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2885</v>
+        <v>211500</v>
       </c>
       <c r="K7" t="n">
-        <v>3000</v>
+        <v>217000</v>
       </c>
       <c r="L7" t="n">
-        <v>3480</v>
+        <v>220000</v>
       </c>
       <c r="M7" t="n">
-        <v>2885</v>
+        <v>216500</v>
       </c>
       <c r="N7" t="n">
-        <v>0.48</v>
+        <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>18404808242</v>
+        <v>540830881250</v>
       </c>
       <c r="P7" t="n">
-        <v>4760</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>973</v>
+        <v>65000</v>
       </c>
       <c r="R7" t="n">
-        <v>-235000</v>
+        <v>276000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유상증자 결정 속에서 주가 변동성 확대. 중간 분석 결과 발표 예정 및 차트 흐름 주목.</t>
+          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유상증자', '중간분석', '차트']</t>
+          <t>['배당', '우선주', '장기보유']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>219000</v>
+        <v>8640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>194</v>
       </c>
       <c r="H8" t="n">
-        <v>75.51000000000001</v>
+        <v>26.63</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>211500</v>
+        <v>8470</v>
       </c>
       <c r="K8" t="n">
-        <v>217000</v>
+        <v>8510</v>
       </c>
       <c r="L8" t="n">
-        <v>220000</v>
+        <v>8870</v>
       </c>
       <c r="M8" t="n">
-        <v>216500</v>
+        <v>8480</v>
       </c>
       <c r="N8" t="n">
-        <v>75.5</v>
+        <v>26.58</v>
       </c>
       <c r="O8" t="n">
-        <v>521752799000</v>
+        <v>15188817180</v>
       </c>
       <c r="P8" t="n">
-        <v>243500</v>
+        <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>65000</v>
+        <v>8120</v>
       </c>
       <c r="R8" t="n">
-        <v>276000</v>
+        <v>359000</v>
       </c>
       <c r="S8" t="n">
-        <v>-25000</v>
+        <v>23000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>장기 보유 및 높은 배당금 기대, JP모건의 목표가 30만원 제시, 외국인 매수에 따른 주가 상승 기대.</t>
+          <t>유리기판 사업 성장성 및 실적 개선 기대감, 외인 매수세 일부 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당', '우선주', 'JP모건']</t>
+          <t>['유리기판', '실적', '외인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8740</v>
+        <v>282000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.19%</t>
+          <t>'+1.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>460</v>
       </c>
       <c r="G9" t="n">
-        <v>179</v>
+        <v>2158</v>
       </c>
       <c r="H9" t="n">
-        <v>26.63</v>
+        <v>46.55</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8470</v>
+        <v>276500</v>
       </c>
       <c r="K9" t="n">
-        <v>8510</v>
+        <v>284500</v>
       </c>
       <c r="L9" t="n">
-        <v>8870</v>
+        <v>285000</v>
       </c>
       <c r="M9" t="n">
-        <v>8480</v>
+        <v>281500</v>
       </c>
       <c r="N9" t="n">
-        <v>26.58</v>
+        <v>46.56</v>
       </c>
       <c r="O9" t="n">
-        <v>13998859435</v>
+        <v>2072192766000</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>8120</v>
+        <v>82400</v>
       </c>
       <c r="R9" t="n">
-        <v>359000</v>
+        <v>1308000</v>
       </c>
       <c r="S9" t="n">
-        <v>23000</v>
+        <v>346000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유리 인터포저 및 유리기판 사업의 구조적 차별화 언급, 부채 상환 부담 및 적자 구조에 대한 우려.</t>
+          <t>HBM 시장 경쟁력 인정 속 개인 매수세 유입 및 연휴 대비 심리 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유리 인터포저', '유리기판', '부채']</t>
+          <t>['HBM', '배당', '연휴']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13900</v>
+        <v>2935</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.21%</t>
+          <t>'+1.73%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.16</v>
+        <v>0.92</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="H10" t="n">
-        <v>9.609999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13600</v>
+        <v>2885</v>
       </c>
       <c r="K10" t="n">
-        <v>13750</v>
+        <v>3000</v>
       </c>
       <c r="L10" t="n">
-        <v>15050</v>
+        <v>3480</v>
       </c>
       <c r="M10" t="n">
-        <v>13750</v>
+        <v>2885</v>
       </c>
       <c r="N10" t="n">
-        <v>9.77</v>
+        <v>0.48</v>
       </c>
       <c r="O10" t="n">
-        <v>81711239380</v>
+        <v>18775458477</v>
       </c>
       <c r="P10" t="n">
-        <v>23550</v>
+        <v>4760</v>
       </c>
       <c r="Q10" t="n">
-        <v>5780</v>
+        <v>973</v>
       </c>
       <c r="R10" t="n">
-        <v>275000</v>
+        <v>-235000</v>
       </c>
       <c r="S10" t="n">
-        <v>-64000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세와 주가 하락에 대한 불만, 도박성 언급이 다수.</t>
+          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['기관', '외인', '하락']</t>
+          <t>['유상증자', '공매도', '차트분석']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>282500</v>
+        <v>13770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.17%</t>
+          <t>'+1.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>456</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>2264</v>
+        <v>156</v>
       </c>
       <c r="H11" t="n">
-        <v>46.55</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>276500</v>
+        <v>13600</v>
       </c>
       <c r="K11" t="n">
-        <v>284500</v>
+        <v>13750</v>
       </c>
       <c r="L11" t="n">
-        <v>285000</v>
+        <v>15050</v>
       </c>
       <c r="M11" t="n">
-        <v>282500</v>
+        <v>13750</v>
       </c>
       <c r="N11" t="n">
-        <v>46.56</v>
+        <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>1940482570250</v>
+        <v>84087300640</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>23550</v>
       </c>
       <c r="Q11" t="n">
-        <v>82400</v>
+        <v>5780</v>
       </c>
       <c r="R11" t="n">
-        <v>1308000</v>
+        <v>275000</v>
       </c>
       <c r="S11" t="n">
-        <v>346000</v>
+        <v>-64000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이재명 대통령 언급과 함께 35만원 목표 제시, JP모건의 HBM 1위 인정 언급.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['HBM', 'JP모건', '배당']</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1857000</v>
+        <v>1849000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.92%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>495</v>
       </c>
       <c r="G12" t="n">
-        <v>1582</v>
+        <v>1556</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1524,13 +1524,13 @@
         <v>1900000</v>
       </c>
       <c r="M12" t="n">
-        <v>1851000</v>
+        <v>1849000</v>
       </c>
       <c r="N12" t="n">
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>2067601378500</v>
+        <v>2212291196500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 반도체주와의 괴리율 언급하며 국내 증시 부진 지적, 200만원대 돌파 기대감.</t>
+          <t>국내 증시 부진 및 외인 매도세에 대한 불만, 미국 증시와의 비교.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['HBM', '반도체', '외국인']</t>
+          <t>['외인', '국장', '미국증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17770</v>
+        <v>31250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.76</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>542</v>
+        <v>111</v>
       </c>
       <c r="H13" t="n">
-        <v>5.46</v>
+        <v>52.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17810</v>
+        <v>31400</v>
       </c>
       <c r="K13" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="L13" t="n">
-        <v>18180</v>
+        <v>32100</v>
       </c>
       <c r="M13" t="n">
-        <v>17410</v>
+        <v>31100</v>
       </c>
       <c r="N13" t="n">
-        <v>6.22</v>
+        <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>101752394045</v>
+        <v>66817865225</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>32100</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>21000</v>
       </c>
       <c r="R13" t="n">
-        <v>-78000</v>
+        <v>29000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>추석 연휴 전 2만원 돌파 기대감 속 쇼티지 및 주포 매집 정황 언급. 단기 과열 경고 가능성 배제.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['쇼티지', '주포', '단기 과열']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31250</v>
+        <v>17690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>-0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>111</v>
+        <v>570</v>
       </c>
       <c r="H14" t="n">
-        <v>52.8</v>
+        <v>5.46</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31400</v>
+        <v>17810</v>
       </c>
       <c r="K14" t="n">
+        <v>17950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18180</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17410</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="O14" t="n">
+        <v>105351135090</v>
+      </c>
+      <c r="P14" t="n">
         <v>31500</v>
       </c>
-      <c r="L14" t="n">
-        <v>32100</v>
-      </c>
-      <c r="M14" t="n">
-        <v>31100</v>
-      </c>
-      <c r="N14" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="O14" t="n">
-        <v>64907419525</v>
-      </c>
-      <c r="P14" t="n">
-        <v>32100</v>
-      </c>
       <c r="Q14" t="n">
-        <v>21000</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>29000</v>
+        <v>-78000</v>
       </c>
       <c r="S14" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>2만원 돌파 기대감 및 쇼티지 현상 언급. 명절 전 거래일 주가 하락 가능성도 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['쇼티지', '명절효과', '주포세력']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31250</v>
+        <v>31000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.11%</t>
+          <t>'-1.90%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H15" t="n">
         <v>11.7</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>44360747300</v>
+        <v>49879782175</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>구리 선물가 및 필지수 상승에 따른 기대감, LS마린과의 비교 및 가온전선과의 주가 흐름 차이 언급.</t>
+          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['구리', 'LS마린', '가온전선']</t>
+          <t>['구리', '텍사스', '가온전선']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="F16" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G16" t="n">
-        <v>1136</v>
+        <v>1256</v>
       </c>
       <c r="H16" t="n">
         <v>16.63</v>
@@ -1892,13 +1892,13 @@
         <v>31550</v>
       </c>
       <c r="M16" t="n">
-        <v>30350</v>
+        <v>30300</v>
       </c>
       <c r="N16" t="n">
         <v>16.42</v>
       </c>
       <c r="O16" t="n">
-        <v>5431805725</v>
+        <v>5869545500</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>간암 및 담관암 신약 FDA 허가 기대감 고조. 릴레이테라퓨틱스 상승 및 HLB 그룹주 동반 상승 전망.</t>
+          <t>간암 신약 FDA 허가 임박 소식 및 릴레이테라퓨틱스 상승. 담관암 결과 및 CRL 관련 논의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['FDA 허가', '리보세라닙', '신약개발']</t>
+          <t>['FDA', '신약허가', '간암']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23400</v>
+        <v>23350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.30%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
         <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H17" t="n">
         <v>1.68</v>
@@ -1990,7 +1990,7 @@
         <v>1.76</v>
       </c>
       <c r="O17" t="n">
-        <v>62487127150</v>
+        <v>63550908375</v>
       </c>
       <c r="P17" t="n">
         <v>39350</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>타임지 세계 최고 헬스테크 기업 선정에도 불구하고 주가 변동성 및 프로그램 매매 동향 주시.</t>
+          <t>타임지 '세계 최고 헬스테크 기업' 선정. 10만까지 상승 기대감 있으나 프로그램 매매 및 눌림목 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '프로그램 매매']</t>
+          <t>['헬스테크', '타임지', '프로그램매매']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>82800</v>
+        <v>48700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.28%</t>
+          <t>'-4.88%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>181</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>930</v>
+        <v>134</v>
       </c>
       <c r="H18" t="n">
-        <v>23.03</v>
+        <v>38.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>86500</v>
+        <v>51200</v>
       </c>
       <c r="K18" t="n">
-        <v>86100</v>
+        <v>51600</v>
       </c>
       <c r="L18" t="n">
-        <v>86100</v>
+        <v>51600</v>
       </c>
       <c r="M18" t="n">
-        <v>82600</v>
+        <v>48700</v>
       </c>
       <c r="N18" t="n">
-        <v>23.05</v>
+        <v>38.44</v>
       </c>
       <c r="O18" t="n">
-        <v>123451353900</v>
+        <v>57961116800</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R18" t="n">
-        <v>-248000</v>
+        <v>-182000</v>
       </c>
       <c r="S18" t="n">
-        <v>-42000</v>
+        <v>-21000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 한국형 원전 2기 수주 확정 소식에도 불구하고 주가 하락세, 투자자들의 불만 제기.</t>
+          <t>20일선 지지 여부에 대한 기대와 실망 반복, 주가 박스권 내에서의 움직임에 대한 답답함 토로.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '수주']</t>
+          <t>['20일선', '박스권', '조정']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48950</v>
+        <v>81800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.39%</t>
+          <t>'-5.43%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="G19" t="n">
-        <v>127</v>
+        <v>1033</v>
       </c>
       <c r="H19" t="n">
-        <v>38.34</v>
+        <v>23.03</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>51200</v>
+        <v>86500</v>
       </c>
       <c r="K19" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="L19" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="M19" t="n">
-        <v>48800</v>
+        <v>81700</v>
       </c>
       <c r="N19" t="n">
-        <v>38.44</v>
+        <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>54700767850</v>
+        <v>140389895650</v>
       </c>
       <c r="P19" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-182000</v>
+        <v>-248000</v>
       </c>
       <c r="S19" t="n">
-        <v>-21000</v>
+        <v>-42000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>20일선 지지 여부에 대한 기대와 실망 반복, 주가 박스권 내에서의 움직임에 대한 답답함 토로.</t>
+          <t>미국 원전 수주 기대감에도 불구하고 외인, 기관 매도세에 따른 주가 하락.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['20일선', '박스권', '조정']</t>
+          <t>['원전', 'SMR', '외인']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17480</v>
+        <v>17460</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.02%</t>
+          <t>'-7.13%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="F20" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G20" t="n">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2260,13 +2260,13 @@
         <v>18800</v>
       </c>
       <c r="M20" t="n">
-        <v>17420</v>
+        <v>17410</v>
       </c>
       <c r="N20" t="n">
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>97540249910</v>
+        <v>102532967920</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력 파산 언급과 함께 대차 해지 운동 촉구, 원전 관련 긍정적 전망.</t>
+          <t>공매도 세력 파산 관련 주장 및 대차 해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공매도', '대차 해지', '원전']</t>
+          <t>['공매도', '대차', '원전']</t>
         </is>
       </c>
       <c r="X20" t="n">
